--- a/MC4010_E24.xlsx
+++ b/MC4010_E24.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{310791FF-673E-426D-8CB2-4B27EDC62C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="MC4010" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -251,9 +250,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -341,10 +340,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -365,7 +364,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -374,12 +373,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -651,7 +651,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -702,7 +702,9 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
-      <c r="H2" s="8"/>
+      <c r="H2" s="8">
+        <v>0</v>
+      </c>
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11">
@@ -721,7 +723,9 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="4"/>
-      <c r="H3" s="8"/>
+      <c r="H3" s="8">
+        <v>81.820000000000007</v>
+      </c>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11">
@@ -740,7 +744,9 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="8"/>
+      <c r="H4" s="8">
+        <v>36.36</v>
+      </c>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11">
@@ -759,7 +765,9 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="8">
+        <v>81.820000000000007</v>
+      </c>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11">
@@ -778,7 +786,9 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="8"/>
+      <c r="H6" s="8">
+        <v>81.820000000000007</v>
+      </c>
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11">
@@ -797,7 +807,9 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="4"/>
-      <c r="H7" s="8"/>
+      <c r="H7" s="8">
+        <v>86.36</v>
+      </c>
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11">
@@ -816,7 +828,9 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="4"/>
-      <c r="H8" s="8"/>
+      <c r="H8" s="8">
+        <v>95.45</v>
+      </c>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11">
@@ -835,7 +849,9 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
-      <c r="H9" s="8"/>
+      <c r="H9" s="8">
+        <v>90.91</v>
+      </c>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11">
@@ -854,7 +870,9 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="4"/>
-      <c r="H10" s="8"/>
+      <c r="H10" s="8">
+        <v>72.72999999999999</v>
+      </c>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11">
@@ -873,7 +891,9 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="4"/>
-      <c r="H11" s="8"/>
+      <c r="H11" s="8">
+        <v>95.45</v>
+      </c>
       <c r="K11" s="1"/>
     </row>
     <row r="12" spans="1:11">
@@ -892,7 +912,9 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="4"/>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8">
+        <v>81.820000000000007</v>
+      </c>
       <c r="K12" s="1"/>
     </row>
     <row r="13" spans="1:11">
@@ -911,7 +933,9 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="4"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="8">
+        <v>95.45</v>
+      </c>
       <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11">
@@ -930,7 +954,9 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="4"/>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8">
+        <v>95.45</v>
+      </c>
       <c r="K14" s="1"/>
     </row>
     <row r="15" spans="1:11">
@@ -949,7 +975,9 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="4"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="8">
+        <v>100</v>
+      </c>
       <c r="K15" s="1"/>
     </row>
     <row r="16" spans="1:11">
@@ -968,7 +996,9 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="4"/>
-      <c r="H16" s="8"/>
+      <c r="H16" s="8">
+        <v>100</v>
+      </c>
       <c r="K16" s="1"/>
     </row>
     <row r="17" spans="1:11">
@@ -987,7 +1017,9 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="4"/>
-      <c r="H17" s="8"/>
+      <c r="H17" s="8">
+        <v>90.91</v>
+      </c>
       <c r="K17" s="1"/>
     </row>
     <row r="18" spans="1:11">
@@ -1006,7 +1038,9 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="4"/>
-      <c r="H18" s="8"/>
+      <c r="H18" s="8">
+        <v>81.820000000000007</v>
+      </c>
       <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:11">
@@ -1025,7 +1059,9 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="4"/>
-      <c r="H19" s="8"/>
+      <c r="H19" s="8">
+        <v>95.45</v>
+      </c>
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:11">
@@ -1044,7 +1080,9 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="4"/>
-      <c r="H20" s="8"/>
+      <c r="H20" s="8">
+        <v>95.45</v>
+      </c>
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="1:11">
@@ -1063,7 +1101,9 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="4"/>
-      <c r="H21" s="8"/>
+      <c r="H21" s="8">
+        <v>90.91</v>
+      </c>
       <c r="K21" s="1"/>
     </row>
     <row r="22" spans="1:11">
@@ -1082,7 +1122,9 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="4"/>
-      <c r="H22" s="8"/>
+      <c r="H22" s="8">
+        <v>86.36</v>
+      </c>
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="1:11">
@@ -1101,7 +1143,9 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="4"/>
-      <c r="H23" s="8"/>
+      <c r="H23" s="8">
+        <v>9.09</v>
+      </c>
       <c r="K23" s="1"/>
     </row>
     <row r="24" spans="1:11">
@@ -1120,7 +1164,9 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="4"/>
-      <c r="H24" s="8"/>
+      <c r="H24" s="8">
+        <v>81.820000000000007</v>
+      </c>
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2" t="s">
@@ -1138,7 +1184,9 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="4"/>
-      <c r="H25" s="8"/>
+      <c r="H25" s="8">
+        <v>86.36</v>
+      </c>
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
@@ -1156,7 +1204,9 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="4"/>
-      <c r="H26" s="8"/>
+      <c r="H26" s="8">
+        <v>77.27000000000001</v>
+      </c>
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2" t="s">
@@ -1174,7 +1224,9 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="4"/>
-      <c r="H27" s="10"/>
+      <c r="H27" s="8">
+        <v>86.36</v>
+      </c>
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2" t="s">
@@ -1192,7 +1244,9 @@
       <c r="E28" s="10"/>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2" t="s">
@@ -1210,7 +1264,9 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
+      <c r="H29" s="8">
+        <v>68.179999999999993</v>
+      </c>
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
@@ -1226,7 +1282,9 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
+      <c r="H30" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2" t="s">
@@ -1244,7 +1302,9 @@
       <c r="E31" s="10"/>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="H31" s="14">
+        <v>9.09</v>
+      </c>
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="6" t="s">
@@ -1260,7 +1320,9 @@
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="H32" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="2" t="s">
@@ -1278,7 +1340,9 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
+      <c r="H33" s="8">
+        <v>40.910000000000004</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1286,9 +1350,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1469,16 +1536,13 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2D6E88-39F5-4606-9F3B-F183017A6423}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9601F5-90FC-4FE2-8653-754DF1EBE00B}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
@@ -1490,7 +1554,7 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BD9601F5-90FC-4FE2-8653-754DF1EBE00B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2D6E88-39F5-4606-9F3B-F183017A6423}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
--- a/MC4010_E24.xlsx
+++ b/MC4010_E24.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BED1BF-F9FD-4773-BAC5-76C7E4B50C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC4010" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -23,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -250,11 +249,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +298,11 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -340,10 +344,10 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -364,7 +368,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -373,13 +377,16 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -651,7 +658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -699,7 +706,9 @@
       <c r="D2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F2" s="5"/>
       <c r="G2" s="4"/>
       <c r="H2" s="8">
@@ -720,7 +729,9 @@
       <c r="D3" s="4">
         <v>90</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="14">
+        <v>71</v>
+      </c>
       <c r="F3" s="5"/>
       <c r="G3" s="4"/>
       <c r="H3" s="8">
@@ -741,7 +752,9 @@
       <c r="D4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F4" s="5"/>
       <c r="G4" s="4"/>
       <c r="H4" s="8">
@@ -762,7 +775,9 @@
       <c r="D5" s="4">
         <v>85</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="14">
+        <v>84</v>
+      </c>
       <c r="F5" s="5"/>
       <c r="G5" s="4"/>
       <c r="H5" s="8">
@@ -783,7 +798,9 @@
       <c r="D6" s="4">
         <v>90</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="14">
+        <v>47</v>
+      </c>
       <c r="F6" s="5"/>
       <c r="G6" s="4"/>
       <c r="H6" s="8">
@@ -804,7 +821,9 @@
       <c r="D7" s="4">
         <v>95</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="14">
+        <v>42</v>
+      </c>
       <c r="F7" s="5"/>
       <c r="G7" s="4"/>
       <c r="H7" s="8">
@@ -825,7 +844,9 @@
       <c r="D8" s="4">
         <v>80</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="14">
+        <v>68</v>
+      </c>
       <c r="F8" s="5"/>
       <c r="G8" s="4"/>
       <c r="H8" s="8">
@@ -846,7 +867,9 @@
       <c r="D9" s="4">
         <v>95</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="14">
+        <v>41</v>
+      </c>
       <c r="F9" s="5"/>
       <c r="G9" s="4"/>
       <c r="H9" s="8">
@@ -867,7 +890,9 @@
       <c r="D10" s="4">
         <v>85</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="14">
+        <v>54</v>
+      </c>
       <c r="F10" s="5"/>
       <c r="G10" s="4"/>
       <c r="H10" s="8">
@@ -888,7 +913,9 @@
       <c r="D11" s="4">
         <v>90</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="14">
+        <v>69</v>
+      </c>
       <c r="F11" s="5"/>
       <c r="G11" s="4"/>
       <c r="H11" s="8">
@@ -909,7 +936,9 @@
       <c r="D12" s="4">
         <v>95</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="14">
+        <v>36</v>
+      </c>
       <c r="F12" s="5"/>
       <c r="G12" s="4"/>
       <c r="H12" s="8">
@@ -930,7 +959,9 @@
       <c r="D13" s="4">
         <v>75</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="14">
+        <v>57</v>
+      </c>
       <c r="F13" s="5"/>
       <c r="G13" s="4"/>
       <c r="H13" s="8">
@@ -951,7 +982,9 @@
       <c r="D14" s="4">
         <v>85</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F14" s="5"/>
       <c r="G14" s="4"/>
       <c r="H14" s="8">
@@ -972,7 +1005,9 @@
       <c r="D15" s="4">
         <v>80</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="14">
+        <v>67</v>
+      </c>
       <c r="F15" s="5"/>
       <c r="G15" s="4"/>
       <c r="H15" s="8">
@@ -993,7 +1028,9 @@
       <c r="D16" s="4">
         <v>85</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="14">
+        <v>69</v>
+      </c>
       <c r="F16" s="5"/>
       <c r="G16" s="4"/>
       <c r="H16" s="8">
@@ -1014,7 +1051,9 @@
       <c r="D17" s="4">
         <v>55</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="14">
+        <v>40</v>
+      </c>
       <c r="F17" s="5"/>
       <c r="G17" s="4"/>
       <c r="H17" s="8">
@@ -1035,7 +1074,9 @@
       <c r="D18" s="4">
         <v>70</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="14">
+        <v>63</v>
+      </c>
       <c r="F18" s="5"/>
       <c r="G18" s="4"/>
       <c r="H18" s="8">
@@ -1056,7 +1097,9 @@
       <c r="D19" s="4">
         <v>80</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="14">
+        <v>61</v>
+      </c>
       <c r="F19" s="5"/>
       <c r="G19" s="4"/>
       <c r="H19" s="8">
@@ -1077,7 +1120,9 @@
       <c r="D20" s="4">
         <v>85</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="14">
+        <v>53</v>
+      </c>
       <c r="F20" s="5"/>
       <c r="G20" s="4"/>
       <c r="H20" s="8">
@@ -1098,7 +1143,9 @@
       <c r="D21" s="4">
         <v>70</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="14">
+        <v>69</v>
+      </c>
       <c r="F21" s="5"/>
       <c r="G21" s="4"/>
       <c r="H21" s="8">
@@ -1119,7 +1166,9 @@
       <c r="D22" s="4">
         <v>55</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="14">
+        <v>72</v>
+      </c>
       <c r="F22" s="5"/>
       <c r="G22" s="4"/>
       <c r="H22" s="8">
@@ -1140,7 +1189,9 @@
       <c r="D23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F23" s="5"/>
       <c r="G23" s="4"/>
       <c r="H23" s="8">
@@ -1161,7 +1212,9 @@
       <c r="D24" s="4">
         <v>95</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="14">
+        <v>63</v>
+      </c>
       <c r="F24" s="5"/>
       <c r="G24" s="4"/>
       <c r="H24" s="8">
@@ -1181,7 +1234,9 @@
       <c r="D25" s="4">
         <v>80</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="14">
+        <v>42</v>
+      </c>
       <c r="F25" s="5"/>
       <c r="G25" s="4"/>
       <c r="H25" s="8">
@@ -1201,7 +1256,9 @@
       <c r="D26" s="4">
         <v>95</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="14">
+        <v>55</v>
+      </c>
       <c r="F26" s="5"/>
       <c r="G26" s="4"/>
       <c r="H26" s="8">
@@ -1221,7 +1278,9 @@
       <c r="D27" s="4">
         <v>45</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="14">
+        <v>32</v>
+      </c>
       <c r="F27" s="5"/>
       <c r="G27" s="4"/>
       <c r="H27" s="8">
@@ -1241,7 +1300,9 @@
       <c r="D28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="10"/>
+      <c r="E28" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F28" s="10"/>
       <c r="G28" s="10"/>
       <c r="H28" s="8">
@@ -1261,7 +1322,9 @@
       <c r="D29" s="4">
         <v>80</v>
       </c>
-      <c r="E29" s="10"/>
+      <c r="E29" s="14">
+        <v>45</v>
+      </c>
       <c r="F29" s="10"/>
       <c r="G29" s="10"/>
       <c r="H29" s="8">
@@ -1279,7 +1342,9 @@
       <c r="D30" s="4">
         <v>70</v>
       </c>
-      <c r="E30" s="10"/>
+      <c r="E30" s="14">
+        <v>48</v>
+      </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="H30" s="8">
@@ -1299,10 +1364,12 @@
       <c r="D31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E31" s="10"/>
+      <c r="E31" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F31" s="10"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="14">
+      <c r="H31" s="15">
         <v>9.09</v>
       </c>
     </row>
@@ -1317,7 +1384,9 @@
       <c r="D32" s="4">
         <v>60</v>
       </c>
-      <c r="E32" s="10"/>
+      <c r="E32" s="14">
+        <v>61</v>
+      </c>
       <c r="F32" s="10"/>
       <c r="G32" s="10"/>
       <c r="H32" s="8">
@@ -1337,7 +1406,9 @@
       <c r="D33" s="4">
         <v>30</v>
       </c>
-      <c r="E33" s="10"/>
+      <c r="E33" s="14" t="s">
+        <v>70</v>
+      </c>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
       <c r="H33" s="8">

--- a/MC4010_E24.xlsx
+++ b/MC4010_E24.xlsx
@@ -5,33 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS_Instrutors\Downloads\New folder (18)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{03BED1BF-F9FD-4773-BAC5-76C7E4B50C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE836A27-FBBF-45B4-9B1A-23D24A936BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MC4010" sheetId="3" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -244,6 +233,12 @@
   </si>
   <si>
     <t>AB</t>
+  </si>
+  <si>
+    <t>DEVINDA S.G.S.</t>
+  </si>
+  <si>
+    <t>BANDARA K.M.J.G.S.C.W.</t>
   </si>
 </sst>
 </file>
@@ -265,14 +260,14 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -302,6 +297,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -347,7 +343,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -359,9 +355,6 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -372,7 +365,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -668,28 +660,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
     </row>
@@ -706,12 +698,16 @@
       <c r="D2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="8">
+      <c r="E2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="7">
         <v>0</v>
       </c>
       <c r="K2" s="1"/>
@@ -729,12 +725,16 @@
       <c r="D3" s="4">
         <v>90</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="12">
         <v>71</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="8">
+      <c r="F3" s="4">
+        <v>91</v>
+      </c>
+      <c r="G3" s="4">
+        <v>92</v>
+      </c>
+      <c r="H3" s="7">
         <v>81.820000000000007</v>
       </c>
       <c r="K3" s="1"/>
@@ -743,7 +743,7 @@
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="4">
@@ -752,12 +752,16 @@
       <c r="D4" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="8">
+      <c r="E4" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="7">
         <v>36.36</v>
       </c>
       <c r="K4" s="1"/>
@@ -775,12 +779,16 @@
       <c r="D5" s="4">
         <v>85</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="12">
         <v>84</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="8">
+      <c r="F5" s="4">
+        <v>72</v>
+      </c>
+      <c r="G5" s="4">
+        <v>84</v>
+      </c>
+      <c r="H5" s="7">
         <v>81.820000000000007</v>
       </c>
       <c r="K5" s="1"/>
@@ -798,12 +806,16 @@
       <c r="D6" s="4">
         <v>90</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <v>47</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="8">
+      <c r="F6" s="4">
+        <v>26</v>
+      </c>
+      <c r="G6" s="4">
+        <v>57</v>
+      </c>
+      <c r="H6" s="7">
         <v>81.820000000000007</v>
       </c>
       <c r="K6" s="1"/>
@@ -821,12 +833,16 @@
       <c r="D7" s="4">
         <v>95</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="12">
         <v>42</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="8">
+      <c r="F7" s="4">
+        <v>82</v>
+      </c>
+      <c r="G7" s="4">
+        <v>94.5</v>
+      </c>
+      <c r="H7" s="7">
         <v>86.36</v>
       </c>
       <c r="K7" s="1"/>
@@ -844,12 +860,16 @@
       <c r="D8" s="4">
         <v>80</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="12">
         <v>68</v>
       </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="8">
+      <c r="F8" s="4">
+        <v>74</v>
+      </c>
+      <c r="G8" s="4">
+        <v>82</v>
+      </c>
+      <c r="H8" s="7">
         <v>95.45</v>
       </c>
       <c r="K8" s="1"/>
@@ -867,12 +887,16 @@
       <c r="D9" s="4">
         <v>95</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="12">
         <v>41</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="8">
+      <c r="F9" s="4">
+        <v>63</v>
+      </c>
+      <c r="G9" s="4">
+        <v>69.5</v>
+      </c>
+      <c r="H9" s="7">
         <v>90.91</v>
       </c>
       <c r="K9" s="1"/>
@@ -890,12 +914,16 @@
       <c r="D10" s="4">
         <v>85</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="12">
         <v>54</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="8">
+      <c r="F10" s="4">
+        <v>70</v>
+      </c>
+      <c r="G10" s="4">
+        <v>79</v>
+      </c>
+      <c r="H10" s="7">
         <v>72.72999999999999</v>
       </c>
       <c r="K10" s="1"/>
@@ -913,12 +941,16 @@
       <c r="D11" s="4">
         <v>90</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="12">
         <v>69</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="8">
+      <c r="F11" s="4">
+        <v>67</v>
+      </c>
+      <c r="G11" s="4">
+        <v>79</v>
+      </c>
+      <c r="H11" s="7">
         <v>95.45</v>
       </c>
       <c r="K11" s="1"/>
@@ -936,12 +968,16 @@
       <c r="D12" s="4">
         <v>95</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="12">
         <v>36</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="8">
+      <c r="F12" s="4">
+        <v>68</v>
+      </c>
+      <c r="G12" s="4">
+        <v>71</v>
+      </c>
+      <c r="H12" s="7">
         <v>81.820000000000007</v>
       </c>
       <c r="K12" s="1"/>
@@ -959,12 +995,16 @@
       <c r="D13" s="4">
         <v>75</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <v>57</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="8">
+      <c r="F13" s="4">
+        <v>95</v>
+      </c>
+      <c r="G13" s="4">
+        <v>91</v>
+      </c>
+      <c r="H13" s="7">
         <v>95.45</v>
       </c>
       <c r="K13" s="1"/>
@@ -982,12 +1022,16 @@
       <c r="D14" s="4">
         <v>85</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="8">
+      <c r="E14" s="12">
+        <v>43</v>
+      </c>
+      <c r="F14" s="4">
+        <v>66</v>
+      </c>
+      <c r="G14" s="4">
+        <v>77.5</v>
+      </c>
+      <c r="H14" s="7">
         <v>95.45</v>
       </c>
       <c r="K14" s="1"/>
@@ -1005,12 +1049,16 @@
       <c r="D15" s="4">
         <v>80</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="12">
         <v>67</v>
       </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="8">
+      <c r="F15" s="4">
+        <v>69</v>
+      </c>
+      <c r="G15" s="4">
+        <v>84</v>
+      </c>
+      <c r="H15" s="7">
         <v>100</v>
       </c>
       <c r="K15" s="1"/>
@@ -1028,12 +1076,16 @@
       <c r="D16" s="4">
         <v>85</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="12">
         <v>69</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="8">
+      <c r="F16" s="4">
+        <v>55</v>
+      </c>
+      <c r="G16" s="4">
+        <v>78.5</v>
+      </c>
+      <c r="H16" s="7">
         <v>100</v>
       </c>
       <c r="K16" s="1"/>
@@ -1051,12 +1103,16 @@
       <c r="D17" s="4">
         <v>55</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="12">
         <v>40</v>
       </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="8">
+      <c r="F17" s="4">
+        <v>10</v>
+      </c>
+      <c r="G17" s="4">
+        <v>47</v>
+      </c>
+      <c r="H17" s="7">
         <v>90.91</v>
       </c>
       <c r="K17" s="1"/>
@@ -1074,12 +1130,16 @@
       <c r="D18" s="4">
         <v>70</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="12">
         <v>63</v>
       </c>
-      <c r="F18" s="5"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="8">
+      <c r="F18" s="4">
+        <v>62</v>
+      </c>
+      <c r="G18" s="4">
+        <v>56</v>
+      </c>
+      <c r="H18" s="7">
         <v>81.820000000000007</v>
       </c>
       <c r="K18" s="1"/>
@@ -1097,12 +1157,16 @@
       <c r="D19" s="4">
         <v>80</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="12">
         <v>61</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="8">
+      <c r="F19" s="4">
+        <v>72</v>
+      </c>
+      <c r="G19" s="4">
+        <v>72.5</v>
+      </c>
+      <c r="H19" s="7">
         <v>95.45</v>
       </c>
       <c r="K19" s="1"/>
@@ -1120,12 +1184,16 @@
       <c r="D20" s="4">
         <v>85</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="12">
         <v>53</v>
       </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="8">
+      <c r="F20" s="4">
+        <v>64</v>
+      </c>
+      <c r="G20" s="4">
+        <v>81</v>
+      </c>
+      <c r="H20" s="7">
         <v>95.45</v>
       </c>
       <c r="K20" s="1"/>
@@ -1143,12 +1211,16 @@
       <c r="D21" s="4">
         <v>70</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="12">
         <v>69</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="8">
+      <c r="F21" s="4">
+        <v>82</v>
+      </c>
+      <c r="G21" s="4">
+        <v>74</v>
+      </c>
+      <c r="H21" s="7">
         <v>90.91</v>
       </c>
       <c r="K21" s="1"/>
@@ -1166,12 +1238,16 @@
       <c r="D22" s="4">
         <v>55</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>72</v>
       </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="8">
+      <c r="F22" s="4">
+        <v>54</v>
+      </c>
+      <c r="G22" s="4">
+        <v>65</v>
+      </c>
+      <c r="H22" s="7">
         <v>86.36</v>
       </c>
       <c r="K22" s="1"/>
@@ -1189,12 +1265,16 @@
       <c r="D23" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="8">
+      <c r="E23" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="7">
         <v>9.09</v>
       </c>
       <c r="K23" s="1"/>
@@ -1212,12 +1292,16 @@
       <c r="D24" s="4">
         <v>95</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>63</v>
       </c>
-      <c r="F24" s="5"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="8">
+      <c r="F24" s="4">
+        <v>61</v>
+      </c>
+      <c r="G24" s="4">
+        <v>54</v>
+      </c>
+      <c r="H24" s="7">
         <v>81.820000000000007</v>
       </c>
     </row>
@@ -1234,12 +1318,16 @@
       <c r="D25" s="4">
         <v>80</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="12">
         <v>42</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="8">
+      <c r="F25" s="4">
+        <v>69</v>
+      </c>
+      <c r="G25" s="4">
+        <v>67</v>
+      </c>
+      <c r="H25" s="7">
         <v>86.36</v>
       </c>
     </row>
@@ -1256,12 +1344,16 @@
       <c r="D26" s="4">
         <v>95</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="12">
         <v>55</v>
       </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="8">
+      <c r="F26" s="4">
+        <v>66</v>
+      </c>
+      <c r="G26" s="4">
+        <v>66.5</v>
+      </c>
+      <c r="H26" s="7">
         <v>77.27000000000001</v>
       </c>
     </row>
@@ -1278,12 +1370,16 @@
       <c r="D27" s="4">
         <v>45</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="12">
         <v>32</v>
       </c>
-      <c r="F27" s="5"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="8">
+      <c r="F27" s="4">
+        <v>25</v>
+      </c>
+      <c r="G27" s="4">
+        <v>42</v>
+      </c>
+      <c r="H27" s="7">
         <v>86.36</v>
       </c>
     </row>
@@ -1300,12 +1396,16 @@
       <c r="D28" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="8">
+      <c r="E28" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1322,12 +1422,16 @@
       <c r="D29" s="4">
         <v>80</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="12">
         <v>45</v>
       </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="8">
+      <c r="F29" s="4">
+        <v>19</v>
+      </c>
+      <c r="G29" s="4">
+        <v>57.5</v>
+      </c>
+      <c r="H29" s="7">
         <v>68.179999999999993</v>
       </c>
     </row>
@@ -1335,19 +1439,25 @@
       <c r="A30" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B30" s="3"/>
+      <c r="B30" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="C30" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D30" s="4">
         <v>70</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="12">
         <v>48</v>
       </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="8">
+      <c r="F30" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G30" s="4">
+        <v>68</v>
+      </c>
+      <c r="H30" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1364,32 +1474,42 @@
       <c r="D31" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="15">
+      <c r="E31" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="13">
         <v>9.09</v>
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="7"/>
+      <c r="B32" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="C32" s="4" t="s">
         <v>70</v>
       </c>
       <c r="D32" s="4">
         <v>60</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="12">
         <v>61</v>
       </c>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="8">
+      <c r="F32" s="4">
+        <v>30</v>
+      </c>
+      <c r="G32" s="4">
+        <v>60.5</v>
+      </c>
+      <c r="H32" s="7">
         <v>0</v>
       </c>
     </row>
@@ -1406,12 +1526,16 @@
       <c r="D33" s="4">
         <v>30</v>
       </c>
-      <c r="E33" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="8">
+      <c r="E33" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="4">
+        <v>45</v>
+      </c>
+      <c r="H33" s="7">
         <v>40.910000000000004</v>
       </c>
     </row>
